--- a/Documentation/Week 7/TimeSheet_Group21_Wk7.xlsx
+++ b/Documentation/Week 7/TimeSheet_Group21_Wk7.xlsx
@@ -5,22 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24314441_student_uwa_edu_au/Documents/UWA/Year 3/Sem 2/CITS3200_Project/Documentation/Week 6/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24314441_student_uwa_edu_au/Documents/UWA/Year 3/Sem 2/CITS3200_Project/Documentation/Week 7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="289" documentId="8_{A2E391BD-BDDC-0249-A3FC-5E810E48BCB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84C88AA6-8ECD-4EAD-AD9D-1FF1DAC60AC2}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_C0971B35128AA1510A92B4E145552F92CDCDE610" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4244F41B-CDF9-4FE8-A715-9A1DC0FD9771}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="1" activeTab="4" xr2:uid="{62AB6E9C-1DC3-774E-B214-74EF319C3060}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="4" r:id="rId1"/>
-    <sheet name="General Tasks" sheetId="1" r:id="rId2"/>
-    <sheet name="Requirements" sheetId="2" r:id="rId3"/>
-    <sheet name="PerPerson" sheetId="5" r:id="rId4"/>
-    <sheet name="Results" sheetId="3" r:id="rId5"/>
+    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="General Tasks" sheetId="2" r:id="rId2"/>
+    <sheet name="Requirements" sheetId="3" r:id="rId3"/>
+    <sheet name="PerPerson" sheetId="4" r:id="rId4"/>
+    <sheet name="Results" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Results!$A$1:$A$18</definedName>
     <definedName name="Tasks">'General Tasks'!$A$11:$A$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -41,35 +40,306 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="139">
+  <si>
+    <t>TOTAL TIME SPENT</t>
+  </si>
+  <si>
+    <t>CALCULATIONS</t>
+  </si>
+  <si>
+    <t>Suggested Total Time to be spent by group =</t>
+  </si>
+  <si>
+    <t>(Computed as 60 hours per person)</t>
+  </si>
+  <si>
+    <t>MET</t>
+  </si>
+  <si>
+    <t>SCRUBBED</t>
+  </si>
+  <si>
+    <t>Actual Total Time Spent By Group =</t>
+  </si>
+  <si>
+    <t>Hours Remaining From Suggested Time Budget =</t>
+  </si>
+  <si>
+    <t>Hours Remaining From Your Groups Chosen Time Budget =</t>
+  </si>
+  <si>
+    <t>Initial Time Estimate  compared to Actual Time Spent =</t>
+  </si>
+  <si>
+    <t>(Taken from week 4)</t>
+  </si>
+  <si>
+    <t>Initial Time Estimate compared to Actual Time Spent =</t>
+  </si>
+  <si>
+    <t>(Taken from week 8)</t>
+  </si>
+  <si>
+    <t>REQUIREMENTS</t>
+  </si>
+  <si>
+    <t>Number of Requirements Met =</t>
+  </si>
+  <si>
+    <t>Value of Requirements Met =</t>
+  </si>
+  <si>
+    <t>Number of Requirements Scrubbed =</t>
+  </si>
+  <si>
+    <t>Value of Requirements Scrubbed =</t>
+  </si>
+  <si>
+    <t>TASKS</t>
+  </si>
+  <si>
+    <t>Number of Tasks Completed =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Tasks Remaining = </t>
+  </si>
+  <si>
+    <t>CITS 3200: Time Analysis Sheet. Semester 2 2008</t>
+  </si>
+  <si>
+    <t>GROUP &lt;NUMBER&gt;</t>
+  </si>
+  <si>
+    <t>MEMBERS:</t>
+  </si>
+  <si>
+    <t>GENERAL INFORMATION</t>
+  </si>
+  <si>
+    <t>This spreadsheet is designed to help your group keep track of the time you have spent on your project, what you have completed and the estimated time you still require to complete specific tasks in your project. Feel free to add tasks but do NOT remove any. Do NOT alter any cells which are coloured RED, or remove anything from the RESULTS worksheet (you may add to the results sheet if you wish)</t>
+  </si>
+  <si>
+    <t>GENERAL TASKS</t>
+  </si>
+  <si>
+    <t>The General Tasks tab records information on the time you spend on specific tasks such as research, learning tools (like Bugzilla) and Documentation</t>
+  </si>
+  <si>
+    <t>Fill in the total time your group wishes to spend on the project - the unit recommends 60hours per person, but some groups may wish to spend a different amount of time to this</t>
+  </si>
+  <si>
+    <t>You may add tasks to the list of tasks - when you add a task record the week number that you added it.</t>
+  </si>
+  <si>
+    <t>Feel free to change the team members responsible for tasks over the course of semester</t>
+  </si>
+  <si>
+    <t>Each week fill in the time your group has spent on each task and the estimate of the time remaining to complete the task</t>
+  </si>
+  <si>
+    <t>Fill in the A cell with the ACTUAL time your group spent on a task the past week</t>
+  </si>
+  <si>
+    <t>Fill in the E cell with the time you ESTIMATE is still needed to complete a task</t>
+  </si>
+  <si>
+    <t>When a task has been completed fill in the completed cell with the week number which you completed it in</t>
+  </si>
+  <si>
+    <t>This Requirements tab records information on the time you spend coding and testing a specific requirement</t>
+  </si>
+  <si>
+    <t>Fill in week added for new Requirements</t>
+  </si>
+  <si>
+    <t>Fill in Team members Responsible</t>
+  </si>
+  <si>
+    <t>Fill in the Difficulty</t>
+  </si>
+  <si>
+    <t>Fill in the Estimated time remaining for coding a requirement</t>
+  </si>
+  <si>
+    <t>Fill in the Actual time you spent on coding the requirement this week</t>
+  </si>
+  <si>
+    <t>Fill in the Estimated time remaining for testing a requirement</t>
+  </si>
+  <si>
+    <t>Fill in the Actual time you spent on testing the requirement this week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you Drop a requirement fill in the week number </t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you Complete a requirement fill in the week number </t>
+  </si>
+  <si>
+    <t>When you enter the clients value for requirements the spreadsheet will check that value sums to $100</t>
+  </si>
+  <si>
+    <t>PERPERSON</t>
+  </si>
+  <si>
+    <t>Each week fill in the total hours each of you have spent working on the project.</t>
+  </si>
+  <si>
+    <t>RESULTS</t>
+  </si>
+  <si>
+    <t>Provides summary statistics on your project, these values are all calculated. Please do NOT alter anything on this worksheet!</t>
+  </si>
+  <si>
+    <t>The Calculations that use deliverable A refer to week 4</t>
+  </si>
+  <si>
+    <t>The Calculations that use deliverable B refer to week 8</t>
+  </si>
+  <si>
+    <t>Suggested total time refers to the units guide of 60 hors per student per semester</t>
+  </si>
+  <si>
+    <t>Feel free to add any calculations that you feel will assist your group in tracking your progress</t>
+  </si>
+  <si>
+    <t>© 2006 Sarah Hatton and Richard Thomas. School of Computer Science and Software Engineering UWA</t>
+  </si>
+  <si>
+    <t>To Do:</t>
+  </si>
+  <si>
+    <t>Fill in the total hours your group has allocated for the project</t>
+  </si>
+  <si>
+    <t>Fill in week added for new tasks</t>
+  </si>
+  <si>
+    <t>Fill in the Estimated time remaining on a task (E)</t>
+  </si>
+  <si>
+    <t>Fill in the Actual time you spent on a task for that week (A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you complete a task fill in the week number </t>
+  </si>
   <si>
     <t>Total Hours our group has allocated =</t>
   </si>
   <si>
-    <t>Fill in the total hours your group has allocated for the project</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">This spreadsheet is designed to help your group keep track of the time you have spent on your project, what you have completed and the estimated time you still require to complete specific tasks in your project. Feel free to add tasks but do NOT remove any. Do NOT alter any cells which are coloured </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">RED, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>or remove anything from the RESULTS worksheet (you may add to the results sheet if you wish)</t>
-    </r>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Time Estimate (hrs) (E=Estimated time remaining, A=Actual time spent this week)</t>
+  </si>
+  <si>
+    <t>Task Name</t>
+  </si>
+  <si>
+    <t>Week Added</t>
+  </si>
+  <si>
+    <t>Team Members Responsible</t>
+  </si>
+  <si>
+    <t>week 2</t>
+  </si>
+  <si>
+    <t>week 3</t>
+  </si>
+  <si>
+    <t>week 4</t>
+  </si>
+  <si>
+    <t>week 5</t>
+  </si>
+  <si>
+    <t>week 6</t>
+  </si>
+  <si>
+    <t>week 7</t>
+  </si>
+  <si>
+    <t>week 8</t>
+  </si>
+  <si>
+    <t>week 9</t>
+  </si>
+  <si>
+    <t>week 10</t>
+  </si>
+  <si>
+    <t>week 11</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>(Week Number)</t>
+  </si>
+  <si>
+    <t>Learning Techniques and tasks (eg bugzilla and CVS)</t>
+  </si>
+  <si>
+    <t>Research and Investigation</t>
+  </si>
+  <si>
+    <t>ALL team members</t>
+  </si>
+  <si>
+    <t>Requirements Gathering</t>
+  </si>
+  <si>
+    <t>Requirements Analysis</t>
+  </si>
+  <si>
+    <t>System Design</t>
+  </si>
+  <si>
+    <t>Test Design</t>
+  </si>
+  <si>
+    <t>Documentation</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>Project Meeting and Communication</t>
+  </si>
+  <si>
+    <t>Review</t>
+  </si>
+  <si>
+    <t>Weekly Client Meetings</t>
+  </si>
+  <si>
+    <t>Team Members who need to attend</t>
+  </si>
+  <si>
+    <t>Sprint 1 Deliverables</t>
+  </si>
+  <si>
+    <t>Dependency Installation</t>
+  </si>
+  <si>
+    <t>Simulation Environment (MuJoCo)</t>
+  </si>
+  <si>
+    <t>Christo, Dhava, Murphy</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Fill in how difficult you think it will be</t>
   </si>
   <si>
     <t>Fill in the Estimated time remaining for coding a requirement (CE)</t>
@@ -84,13 +354,49 @@
     <t>Fill in the Actual time you spent on testing the requirement this week (TA)</t>
   </si>
   <si>
-    <t>Fill in the Estimated time remaining on a task (E)</t>
-  </si>
-  <si>
-    <t>Fill in the Actual time you spent on a task for that week (A)</t>
+    <t>The cell below checks that your Value sums to $100</t>
+  </si>
+  <si>
+    <t>Requirement Name</t>
+  </si>
+  <si>
+    <t>Client Value ($)</t>
+  </si>
+  <si>
+    <t>Time (CE = Code Estimated Time Remaining, CA = Actual Time Spent Coding This Week, TE= Testing Estimated Time Remaining, TA= Actual Time Spent Testing This Week)</t>
   </si>
   <si>
     <t>difficulty</t>
+  </si>
+  <si>
+    <t>Week 2</t>
+  </si>
+  <si>
+    <t>Week 3</t>
+  </si>
+  <si>
+    <t>Week 4</t>
+  </si>
+  <si>
+    <t>Week 5</t>
+  </si>
+  <si>
+    <t>Week 6</t>
+  </si>
+  <si>
+    <t>Week 7</t>
+  </si>
+  <si>
+    <t>Week 8</t>
+  </si>
+  <si>
+    <t>Week 9</t>
+  </si>
+  <si>
+    <t>Week 10</t>
+  </si>
+  <si>
+    <t>Week 11</t>
   </si>
   <si>
     <t>dropped (week)</t>
@@ -104,37 +410,31 @@
 3-hard</t>
   </si>
   <si>
-    <t>Fill in how difficult you think it will be</t>
-  </si>
-  <si>
-    <t>Initial Time Estimate compared to Actual Time Spent =</t>
-  </si>
-  <si>
-    <t>Initial Time Estimate  compared to Actual Time Spent =</t>
-  </si>
-  <si>
-    <t>Fill in the Difficulty</t>
-  </si>
-  <si>
-    <t>CITS 3200: Time Analysis Sheet. Semester 2 2008</t>
-  </si>
-  <si>
-    <t>Fill in the Estimated time remaining for coding a requirement</t>
-  </si>
-  <si>
-    <t>Fill in the Actual time you spent on testing the requirement this week</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If you Drop a requirement fill in the week number </t>
-  </si>
-  <si>
-    <t xml:space="preserve">If you Complete a requirement fill in the week number </t>
-  </si>
-  <si>
-    <t>REQUIREMENTS</t>
-  </si>
-  <si>
-    <t>This Requirements tab records information on the time you spend coding and testing a specific requirement</t>
+    <t>CE</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>TE</t>
+  </si>
+  <si>
+    <t>TA</t>
+  </si>
+  <si>
+    <t>Gesture Recognition Program</t>
+  </si>
+  <si>
+    <t>Christo, Murphy, Terry</t>
+  </si>
+  <si>
+    <t>Person Tracking and Recognition Program</t>
+  </si>
+  <si>
+    <t>Dylan, Lithasa, Dhava</t>
+  </si>
+  <si>
+    <t>TO DO:</t>
   </si>
   <si>
     <t>Total Hours</t>
@@ -143,436 +443,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Each week fill in the total hours each of you have spent working on the project.</t>
-  </si>
-  <si>
-    <t>PERPERSON</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>RESULTS</t>
-  </si>
-  <si>
-    <t>Provides summary statistics on your project, these values are all calculated. Please do NOT alter anything on this worksheet!</t>
-  </si>
-  <si>
-    <t>TOTAL TIME SPENT</t>
-  </si>
-  <si>
-    <t>Suggested Total Time to be spent by group =</t>
-  </si>
-  <si>
-    <t>Actual Total Time Spent By Group =</t>
-  </si>
-  <si>
-    <t>Hours Remaining From Suggested Time Budget =</t>
-  </si>
-  <si>
-    <t>Value of Requirements Met =</t>
-  </si>
-  <si>
-    <t>Number of Requirements Met =</t>
-  </si>
-  <si>
-    <t>Number of Requirements Scrubbed =</t>
-  </si>
-  <si>
-    <t>Value of Requirements Scrubbed =</t>
-  </si>
-  <si>
-    <t>TASKS</t>
-  </si>
-  <si>
-    <t>CALCULATIONS</t>
-  </si>
-  <si>
-    <t>MET</t>
-  </si>
-  <si>
-    <t>SCRUBBED</t>
-  </si>
-  <si>
-    <t>Number of Tasks Completed =</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of Tasks Remaining = </t>
-  </si>
-  <si>
-    <t>When you enter the clients value for requirements the spreadsheet will check that value sums to $100</t>
-  </si>
-  <si>
-    <t>The cell below checks that your Value sums to $100</t>
-  </si>
-  <si>
-    <t>© 2006 Sarah Hatton and Richard Thomas. School of Computer Science and Software Engineering UWA</t>
-  </si>
-  <si>
-    <t>TO DO:</t>
-  </si>
-  <si>
-    <t>(Computed as 60 hours per person)</t>
-  </si>
-  <si>
-    <t>(Taken from week 4)</t>
-  </si>
-  <si>
-    <t>(Taken from week 8)</t>
-  </si>
-  <si>
-    <t>The Calculations that use deliverable A refer to week 4</t>
-  </si>
-  <si>
-    <t>The Calculations that use deliverable B refer to week 8</t>
-  </si>
-  <si>
-    <t>Suggested total time refers to the units guide of 60 hors per student per semester</t>
-  </si>
-  <si>
-    <t>Fill in the total time your group wishes to spend on the project - the unit recommends 60hours per person, but some groups may wish to spend a different amount of time to this</t>
-  </si>
-  <si>
-    <t>Feel free to add any calculations that you feel will assist your group in tracking your progress</t>
-  </si>
-  <si>
-    <t>Hours Remaining From Your Groups Chosen Time Budget =</t>
-  </si>
-  <si>
-    <t>Task</t>
-  </si>
-  <si>
-    <t>Task Name</t>
-  </si>
-  <si>
-    <t>Week Added</t>
-  </si>
-  <si>
-    <t>week 2</t>
-  </si>
-  <si>
-    <t>week 3</t>
-  </si>
-  <si>
-    <t>week 4</t>
-  </si>
-  <si>
-    <t>week 5</t>
-  </si>
-  <si>
-    <t>week 6</t>
-  </si>
-  <si>
-    <t>week 7</t>
-  </si>
-  <si>
-    <t>week 8</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>week 9</t>
-  </si>
-  <si>
-    <t>week 10</t>
-  </si>
-  <si>
-    <t>week 11</t>
-  </si>
-  <si>
-    <t>Completed</t>
-  </si>
-  <si>
-    <t>(Week Number)</t>
-  </si>
-  <si>
-    <r>
-      <t>Time Estimate (hrs) (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color indexed="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>E=Estimated time remaining</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color indexed="17"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A=Actual time spent this week</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>GROUP &lt;NUMBER&gt;</t>
-  </si>
-  <si>
-    <t>GENERAL INFORMATION</t>
-  </si>
-  <si>
-    <t>MEMBERS:</t>
-  </si>
-  <si>
-    <t>GENERAL TASKS</t>
-  </si>
-  <si>
-    <t>The General Tasks tab records information on the time you spend on specific tasks such as research, learning tools (like Bugzilla) and Documentation</t>
-  </si>
-  <si>
-    <t>You may add tasks to the list of tasks - when you add a task record the week number that you added it.</t>
-  </si>
-  <si>
-    <t>Feel free to change the team members responsible for tasks over the course of semester</t>
-  </si>
-  <si>
-    <t>Each week fill in the time your group has spent on each task and the estimate of the time remaining to complete the task</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">When a task has been completed fill in the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>completed cell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> with the week number which you completed it in</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Fill in the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>E cell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> with the time you ESTIMATE is still needed to complete a task</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Fill in the </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A cell</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> with the ACTUAL time your group spent on a task the past week</t>
-    </r>
-  </si>
-  <si>
-    <t>Requirement Name</t>
-  </si>
-  <si>
-    <t>Week 2</t>
-  </si>
-  <si>
-    <t>Week 3</t>
-  </si>
-  <si>
-    <t>Week 4</t>
-  </si>
-  <si>
-    <t>Week 5</t>
-  </si>
-  <si>
-    <t>Week 6</t>
-  </si>
-  <si>
-    <t>Week 7</t>
-  </si>
-  <si>
-    <t>Week 8</t>
-  </si>
-  <si>
-    <t>Week 9</t>
-  </si>
-  <si>
-    <t>Week 10</t>
-  </si>
-  <si>
-    <t>Week 11</t>
-  </si>
-  <si>
-    <t>CE</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>TE</t>
-  </si>
-  <si>
-    <t>TA</t>
-  </si>
-  <si>
-    <t>Client Value ($)</t>
-  </si>
-  <si>
-    <r>
-      <t>Time (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color indexed="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>CE = Code Estimated Time Remaining</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color indexed="17"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>CA = Actual Time Spent Coding This Week</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color indexed="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> TE= Testing Estimated Time Remaining</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color indexed="52"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>TA= Actual Time Spent Testing This Week</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Fill in week added for new tasks</t>
-  </si>
-  <si>
-    <t>Fill in Team members Responsible</t>
-  </si>
-  <si>
-    <t>To Do:</t>
-  </si>
-  <si>
-    <t>Fill in week added for new Requirements</t>
-  </si>
-  <si>
-    <t>Team Members Responsible</t>
-  </si>
-  <si>
-    <t>Fill in the Actual time you spent on coding the requirement this week</t>
-  </si>
-  <si>
-    <t>Fill in the Estimated time remaining for testing a requirement</t>
-  </si>
-  <si>
     <t>Christo Wesseloo</t>
   </si>
   <si>
@@ -589,73 +459,13 @@
   </si>
   <si>
     <t>Murphy Chen</t>
-  </si>
-  <si>
-    <t>ALL team members</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If you complete a task fill in the week number </t>
-  </si>
-  <si>
-    <t>Weekly Client Meetings</t>
-  </si>
-  <si>
-    <t>Project Manager</t>
-  </si>
-  <si>
-    <t>Learning Techniques and tasks (eg bugzilla and CVS)</t>
-  </si>
-  <si>
-    <t>Research and Investigation</t>
-  </si>
-  <si>
-    <t>Requirements Gathering</t>
-  </si>
-  <si>
-    <t>Requirements Analysis</t>
-  </si>
-  <si>
-    <t>System Design</t>
-  </si>
-  <si>
-    <t>Test Design</t>
-  </si>
-  <si>
-    <t>Documentation</t>
-  </si>
-  <si>
-    <t>Project Meeting and Communication</t>
-  </si>
-  <si>
-    <t>Review</t>
-  </si>
-  <si>
-    <t>Gesture Recognition Program</t>
-  </si>
-  <si>
-    <t>Christo, Murphy, Terry</t>
-  </si>
-  <si>
-    <t>Dylan, Lithasa, Dhava</t>
-  </si>
-  <si>
-    <t>Person Tracking and Recognition Program</t>
-  </si>
-  <si>
-    <t>Team Members who need to attend</t>
-  </si>
-  <si>
-    <t>Sprint 1 Deliverables</t>
-  </si>
-  <si>
-    <t>Dependency Installation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -681,11 +491,6 @@
       <b/>
       <i/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -754,12 +559,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color indexed="10"/>
@@ -776,12 +575,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -988,10 +781,10 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
-      </top>
-      <bottom/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1002,16 +795,14 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1034,17 +825,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1053,40 +844,40 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1117,20 +908,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1142,13 +933,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1160,49 +951,40 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1210,101 +992,48 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1855,7 +1584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E65ABAE-D99C-A043-8E5B-109120B67823}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor indexed="22"/>
   </sheetPr>
@@ -1863,102 +1592,102 @@
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
+      <c r="A1" s="79" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="69"/>
+      <c r="I1" s="69"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="69"/>
+      <c r="L1" s="69"/>
+      <c r="M1" s="69"/>
+      <c r="N1" s="69"/>
+      <c r="O1" s="69"/>
+      <c r="P1" s="69"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="75"/>
-      <c r="N2" s="75"/>
-      <c r="O2" s="75"/>
-      <c r="P2" s="75"/>
+      <c r="A2" s="69"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="79"/>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-    </row>
-    <row r="4" spans="1:16" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A4" s="81" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="81"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="81"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="81"/>
-      <c r="M4" s="81"/>
-      <c r="N4" s="81"/>
-      <c r="O4" s="81"/>
-      <c r="P4" s="81"/>
-    </row>
-    <row r="5" spans="1:16" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A5" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="81"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="81"/>
-      <c r="O5" s="81"/>
-      <c r="P5" s="81"/>
-    </row>
-    <row r="6" spans="1:16" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A3" s="69"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="69"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="69"/>
+    </row>
+    <row r="4" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="93" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="69"/>
+      <c r="P4" s="69"/>
+    </row>
+    <row r="5" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="93" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="69"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="69"/>
+      <c r="P5" s="69"/>
+    </row>
+    <row r="6" spans="1:16" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -1977,83 +1706,83 @@
       <c r="P6" s="8"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="83" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="84"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="84"/>
-      <c r="J7" s="84"/>
-      <c r="K7" s="84"/>
-      <c r="L7" s="84"/>
-      <c r="M7" s="84"/>
+      <c r="A7" s="82" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="69"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="82" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="82"/>
-      <c r="J8" s="82"/>
-      <c r="K8" s="82"/>
-      <c r="L8" s="82"/>
-      <c r="M8" s="82"/>
+      <c r="A8" s="81" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="82"/>
-      <c r="B9" s="82"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="82"/>
-      <c r="F9" s="82"/>
-      <c r="G9" s="82"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="82"/>
-      <c r="J9" s="82"/>
-      <c r="K9" s="82"/>
-      <c r="L9" s="82"/>
-      <c r="M9" s="82"/>
+      <c r="A9" s="69"/>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="69"/>
+      <c r="M9" s="69"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="82"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="82"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="82"/>
-      <c r="H10" s="82"/>
-      <c r="I10" s="82"/>
-      <c r="J10" s="82"/>
-      <c r="K10" s="82"/>
-      <c r="L10" s="82"/>
-      <c r="M10" s="82"/>
+      <c r="A10" s="69"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="69"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="69"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="82"/>
-      <c r="B11" s="82"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="82"/>
-      <c r="F11" s="82"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="82"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="82"/>
-      <c r="L11" s="82"/>
-      <c r="M11" s="82"/>
+      <c r="A11" s="69"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
+      <c r="K11" s="69"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="69"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="53"/>
@@ -2071,187 +1800,187 @@
       <c r="M12" s="53"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="76" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="76"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="76"/>
-      <c r="L14" s="76"/>
-      <c r="M14" s="76"/>
+      <c r="A14" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="69"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="69"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="77" t="s">
-        <v>80</v>
-      </c>
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="77"/>
-      <c r="K15" s="77"/>
-      <c r="L15" s="77"/>
-      <c r="M15" s="77"/>
+      <c r="A15" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="69"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="69"/>
+      <c r="M15" s="69"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="77"/>
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="77"/>
-      <c r="K16" s="77"/>
-      <c r="L16" s="77"/>
-      <c r="M16" s="77"/>
+      <c r="A16" s="69"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="69"/>
+      <c r="M16" s="69"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="77" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="77"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="77"/>
-      <c r="K17" s="77"/>
-      <c r="L17" s="77"/>
-      <c r="M17" s="77"/>
+      <c r="A17" s="80" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="69"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="69"/>
+      <c r="M17" s="69"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="79"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="79"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="79"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="79"/>
-      <c r="K18" s="79"/>
-      <c r="L18" s="79"/>
-      <c r="M18" s="79"/>
+      <c r="A18" s="69"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69"/>
+      <c r="L18" s="69"/>
+      <c r="M18" s="69"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="78" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="77"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="77"/>
-      <c r="K19" s="77"/>
-      <c r="L19" s="77"/>
-      <c r="M19" s="77"/>
+      <c r="A19" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="69"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
+      <c r="L19" s="69"/>
+      <c r="M19" s="69"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="78" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="77"/>
-      <c r="C20" s="77"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="77"/>
-      <c r="K20" s="77"/>
-      <c r="L20" s="77"/>
-      <c r="M20" s="77"/>
+      <c r="A20" s="86" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="69"/>
+      <c r="C20" s="69"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="69"/>
+      <c r="L20" s="69"/>
+      <c r="M20" s="69"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="78" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="77"/>
-      <c r="C21" s="77"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="77"/>
-      <c r="L21" s="77"/>
-      <c r="M21" s="77"/>
+      <c r="A21" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="69"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="69"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="69"/>
+      <c r="K21" s="69"/>
+      <c r="L21" s="69"/>
+      <c r="M21" s="69"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="77" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="77"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="77"/>
-      <c r="M22" s="77"/>
+      <c r="A22" s="80" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="69"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="69"/>
+      <c r="L22" s="69"/>
+      <c r="M22" s="69"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="77" t="s">
-        <v>85</v>
-      </c>
-      <c r="B23" s="77"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="77"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="77"/>
-      <c r="K23" s="77"/>
-      <c r="L23" s="77"/>
-      <c r="M23" s="77"/>
+      <c r="A23" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="69"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="69"/>
+      <c r="M23" s="69"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="77" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="77"/>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="77"/>
-      <c r="K24" s="77"/>
-      <c r="L24" s="77"/>
-      <c r="M24" s="77"/>
+      <c r="A24" s="80" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="69"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="69"/>
+      <c r="K24" s="69"/>
+      <c r="L24" s="69"/>
+      <c r="M24" s="69"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="52"/>
@@ -2269,208 +1998,208 @@
       <c r="M25" s="52"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="88" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="88"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="68"/>
-      <c r="H27" s="68"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="68"/>
-      <c r="K27" s="68"/>
-      <c r="L27" s="68"/>
-      <c r="M27" s="68"/>
+      <c r="A27" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="69"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="69"/>
+      <c r="L27" s="69"/>
+      <c r="M27" s="69"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="71" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="89"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
-      <c r="L28" s="89"/>
-      <c r="M28" s="89"/>
+      <c r="A28" s="84" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="69"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
+      <c r="F28" s="69"/>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="69"/>
+      <c r="L28" s="69"/>
+      <c r="M28" s="69"/>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="69" t="s">
-        <v>107</v>
+      <c r="A29" s="88" t="s">
+        <v>36</v>
       </c>
       <c r="B29" s="69"/>
       <c r="C29" s="69"/>
       <c r="D29" s="69"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="72"/>
-      <c r="G29" s="72"/>
-      <c r="H29" s="72"/>
-      <c r="I29" s="72"/>
-      <c r="J29" s="72"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="72"/>
-      <c r="M29" s="72"/>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69"/>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="69"/>
+      <c r="J29" s="69"/>
+      <c r="K29" s="69"/>
+      <c r="L29" s="69"/>
+      <c r="M29" s="69"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="69" t="s">
-        <v>105</v>
+      <c r="A30" s="88" t="s">
+        <v>37</v>
       </c>
       <c r="B30" s="69"/>
       <c r="C30" s="69"/>
       <c r="D30" s="69"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="70"/>
-      <c r="K30" s="70"/>
-      <c r="L30" s="70"/>
-      <c r="M30" s="70"/>
+      <c r="E30" s="69"/>
+      <c r="F30" s="69"/>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="69"/>
+      <c r="J30" s="69"/>
+      <c r="K30" s="69"/>
+      <c r="L30" s="69"/>
+      <c r="M30" s="69"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="69" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" s="75"/>
-      <c r="C31" s="75"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="75"/>
-      <c r="M31" s="75"/>
+      <c r="A31" s="88" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="69"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+      <c r="I31" s="69"/>
+      <c r="J31" s="69"/>
+      <c r="K31" s="69"/>
+      <c r="L31" s="69"/>
+      <c r="M31" s="69"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="69" t="s">
-        <v>18</v>
+      <c r="A32" s="88" t="s">
+        <v>39</v>
       </c>
       <c r="B32" s="69"/>
       <c r="C32" s="69"/>
       <c r="D32" s="69"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="70"/>
-      <c r="J32" s="70"/>
-      <c r="K32" s="70"/>
-      <c r="L32" s="70"/>
-      <c r="M32" s="70"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="69"/>
+      <c r="G32" s="69"/>
+      <c r="H32" s="69"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="69"/>
+      <c r="K32" s="69"/>
+      <c r="L32" s="69"/>
+      <c r="M32" s="69"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="71" t="s">
-        <v>109</v>
-      </c>
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="70"/>
-      <c r="F33" s="70"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="70"/>
-      <c r="I33" s="70"/>
-      <c r="J33" s="70"/>
-      <c r="K33" s="70"/>
-      <c r="L33" s="70"/>
-      <c r="M33" s="70"/>
+      <c r="A33" s="84" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="69"/>
+      <c r="C33" s="69"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
+      <c r="F33" s="69"/>
+      <c r="G33" s="69"/>
+      <c r="H33" s="69"/>
+      <c r="I33" s="69"/>
+      <c r="J33" s="69"/>
+      <c r="K33" s="69"/>
+      <c r="L33" s="69"/>
+      <c r="M33" s="69"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="69" t="s">
-        <v>110</v>
+      <c r="A34" s="88" t="s">
+        <v>41</v>
       </c>
       <c r="B34" s="69"/>
       <c r="C34" s="69"/>
       <c r="D34" s="69"/>
-      <c r="E34" s="70"/>
-      <c r="F34" s="70"/>
-      <c r="G34" s="70"/>
-      <c r="H34" s="70"/>
-      <c r="I34" s="70"/>
-      <c r="J34" s="70"/>
-      <c r="K34" s="70"/>
-      <c r="L34" s="70"/>
-      <c r="M34" s="70"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="69"/>
+      <c r="K34" s="69"/>
+      <c r="L34" s="69"/>
+      <c r="M34" s="69"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="71" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
-      <c r="I35" s="70"/>
-      <c r="J35" s="70"/>
-      <c r="K35" s="70"/>
-      <c r="L35" s="70"/>
-      <c r="M35" s="70"/>
+      <c r="A35" s="84" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="69"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="69"/>
+      <c r="L35" s="69"/>
+      <c r="M35" s="69"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="71" t="s">
-        <v>20</v>
-      </c>
-      <c r="B36" s="71"/>
-      <c r="C36" s="71"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="70"/>
-      <c r="K36" s="70"/>
-      <c r="L36" s="70"/>
-      <c r="M36" s="70"/>
+      <c r="A36" s="84" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="69"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="69"/>
+      <c r="K36" s="69"/>
+      <c r="L36" s="69"/>
+      <c r="M36" s="69"/>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="71" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37" s="71"/>
-      <c r="C37" s="71"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="70"/>
-      <c r="F37" s="70"/>
-      <c r="G37" s="70"/>
-      <c r="H37" s="70"/>
-      <c r="I37" s="70"/>
-      <c r="J37" s="70"/>
-      <c r="K37" s="70"/>
-      <c r="L37" s="70"/>
-      <c r="M37" s="70"/>
+      <c r="A37" s="84" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="69"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="69"/>
+      <c r="K37" s="69"/>
+      <c r="L37" s="69"/>
+      <c r="M37" s="69"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="71" t="s">
+      <c r="A38" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="68"/>
-      <c r="C38" s="68"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
-      <c r="H38" s="68"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="68"/>
-      <c r="M38" s="68"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="69"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="69"/>
+      <c r="F38" s="69"/>
+      <c r="G38" s="69"/>
+      <c r="H38" s="69"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="69"/>
+      <c r="K38" s="69"/>
+      <c r="L38" s="69"/>
+      <c r="M38" s="69"/>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="51"/>
@@ -2488,38 +2217,38 @@
       <c r="M39" s="59"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="74"/>
-      <c r="C41" s="74"/>
-      <c r="D41" s="74"/>
-      <c r="E41" s="74"/>
-      <c r="F41" s="74"/>
-      <c r="G41" s="74"/>
-      <c r="H41" s="74"/>
-      <c r="I41" s="74"/>
-      <c r="J41" s="74"/>
-      <c r="K41" s="74"/>
-      <c r="L41" s="74"/>
-      <c r="M41" s="74"/>
+      <c r="A41" s="83" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="69"/>
+      <c r="C41" s="69"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
+      <c r="F41" s="69"/>
+      <c r="G41" s="69"/>
+      <c r="H41" s="69"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="69"/>
+      <c r="K41" s="69"/>
+      <c r="L41" s="69"/>
+      <c r="M41" s="69"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="67" t="s">
-        <v>26</v>
-      </c>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
-      <c r="H42" s="68"/>
-      <c r="I42" s="68"/>
-      <c r="J42" s="68"/>
-      <c r="K42" s="68"/>
-      <c r="L42" s="68"/>
-      <c r="M42" s="68"/>
+      <c r="A42" s="92" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="69"/>
+      <c r="C42" s="69"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="69"/>
+      <c r="F42" s="69"/>
+      <c r="G42" s="69"/>
+      <c r="H42" s="69"/>
+      <c r="I42" s="69"/>
+      <c r="J42" s="69"/>
+      <c r="K42" s="69"/>
+      <c r="L42" s="69"/>
+      <c r="M42" s="69"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="50"/>
@@ -2542,106 +2271,106 @@
       <c r="C44" s="7"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="86" t="s">
-        <v>29</v>
-      </c>
-      <c r="B45" s="87"/>
-      <c r="C45" s="87"/>
-      <c r="D45" s="87"/>
-      <c r="E45" s="87"/>
-      <c r="F45" s="87"/>
-      <c r="G45" s="87"/>
-      <c r="H45" s="87"/>
-      <c r="I45" s="87"/>
-      <c r="J45" s="87"/>
-      <c r="K45" s="87"/>
-      <c r="L45" s="87"/>
-      <c r="M45" s="87"/>
+      <c r="A45" s="91" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="69"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="69"/>
+      <c r="K45" s="69"/>
+      <c r="L45" s="69"/>
+      <c r="M45" s="69"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="91" t="s">
-        <v>30</v>
-      </c>
-      <c r="B46" s="91"/>
-      <c r="C46" s="91"/>
-      <c r="D46" s="91"/>
-      <c r="E46" s="91"/>
-      <c r="F46" s="91"/>
-      <c r="G46" s="91"/>
-      <c r="H46" s="91"/>
-      <c r="I46" s="91"/>
-      <c r="J46" s="91"/>
-      <c r="K46" s="91"/>
-      <c r="L46" s="91"/>
-      <c r="M46" s="91"/>
+      <c r="A46" s="89" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" s="69"/>
+      <c r="C46" s="69"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
+      <c r="F46" s="69"/>
+      <c r="G46" s="69"/>
+      <c r="H46" s="69"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="69"/>
+      <c r="K46" s="69"/>
+      <c r="L46" s="69"/>
+      <c r="M46" s="69"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="91" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47" s="91"/>
-      <c r="C47" s="91"/>
-      <c r="D47" s="91"/>
-      <c r="E47" s="91"/>
-      <c r="F47" s="91"/>
-      <c r="G47" s="91"/>
-      <c r="H47" s="91"/>
-      <c r="I47" s="91"/>
-      <c r="J47" s="91"/>
-      <c r="K47" s="91"/>
-      <c r="L47" s="91"/>
-      <c r="M47" s="91"/>
+      <c r="A47" s="89" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="69"/>
+      <c r="C47" s="69"/>
+      <c r="D47" s="69"/>
+      <c r="E47" s="69"/>
+      <c r="F47" s="69"/>
+      <c r="G47" s="69"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="69"/>
+      <c r="J47" s="69"/>
+      <c r="K47" s="69"/>
+      <c r="L47" s="69"/>
+      <c r="M47" s="69"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="91" t="s">
-        <v>53</v>
-      </c>
-      <c r="B48" s="91"/>
-      <c r="C48" s="91"/>
-      <c r="D48" s="91"/>
-      <c r="E48" s="91"/>
-      <c r="F48" s="91"/>
-      <c r="G48" s="91"/>
-      <c r="H48" s="91"/>
-      <c r="I48" s="91"/>
-      <c r="J48" s="91"/>
-      <c r="K48" s="91"/>
-      <c r="L48" s="91"/>
-      <c r="M48" s="91"/>
+      <c r="A48" s="89" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="69"/>
+      <c r="C48" s="69"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="69"/>
+      <c r="H48" s="69"/>
+      <c r="I48" s="69"/>
+      <c r="J48" s="69"/>
+      <c r="K48" s="69"/>
+      <c r="L48" s="69"/>
+      <c r="M48" s="69"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="90" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" s="90"/>
-      <c r="C49" s="90"/>
-      <c r="D49" s="90"/>
-      <c r="E49" s="90"/>
-      <c r="F49" s="90"/>
-      <c r="G49" s="90"/>
-      <c r="H49" s="90"/>
-      <c r="I49" s="90"/>
-      <c r="J49" s="90"/>
-      <c r="K49" s="90"/>
-      <c r="L49" s="90"/>
-      <c r="M49" s="90"/>
+        <v>52</v>
+      </c>
+      <c r="B49" s="69"/>
+      <c r="C49" s="69"/>
+      <c r="D49" s="69"/>
+      <c r="E49" s="69"/>
+      <c r="F49" s="69"/>
+      <c r="G49" s="69"/>
+      <c r="H49" s="69"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="69"/>
+      <c r="K49" s="69"/>
+      <c r="L49" s="69"/>
+      <c r="M49" s="69"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="90"/>
-      <c r="C50" s="90"/>
-      <c r="D50" s="90"/>
-      <c r="E50" s="90"/>
-      <c r="F50" s="90"/>
-      <c r="G50" s="90"/>
-      <c r="H50" s="90"/>
-      <c r="I50" s="90"/>
-      <c r="J50" s="90"/>
-      <c r="K50" s="90"/>
-      <c r="L50" s="90"/>
-      <c r="M50" s="90"/>
+        <v>53</v>
+      </c>
+      <c r="B50" s="69"/>
+      <c r="C50" s="69"/>
+      <c r="D50" s="69"/>
+      <c r="E50" s="69"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="69"/>
+      <c r="H50" s="69"/>
+      <c r="I50" s="69"/>
+      <c r="J50" s="69"/>
+      <c r="K50" s="69"/>
+      <c r="L50" s="69"/>
+      <c r="M50" s="69"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="55"/>
@@ -2689,126 +2418,124 @@
       <c r="M53" s="58"/>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A54" s="85" t="s">
-        <v>47</v>
-      </c>
-      <c r="B54" s="85"/>
-      <c r="C54" s="85"/>
-      <c r="D54" s="85"/>
-      <c r="E54" s="85"/>
-      <c r="F54" s="85"/>
-      <c r="G54" s="85"/>
-      <c r="H54" s="85"/>
-      <c r="I54" s="85"/>
-      <c r="J54" s="85"/>
-      <c r="K54" s="85"/>
-      <c r="L54" s="85"/>
-      <c r="M54" s="85"/>
-      <c r="N54" s="85"/>
-      <c r="O54" s="85"/>
-      <c r="P54" s="85"/>
+      <c r="A54" s="87" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54" s="69"/>
+      <c r="C54" s="69"/>
+      <c r="D54" s="69"/>
+      <c r="E54" s="69"/>
+      <c r="F54" s="69"/>
+      <c r="G54" s="69"/>
+      <c r="H54" s="69"/>
+      <c r="I54" s="69"/>
+      <c r="J54" s="69"/>
+      <c r="K54" s="69"/>
+      <c r="L54" s="69"/>
+      <c r="M54" s="69"/>
+      <c r="N54" s="69"/>
+      <c r="O54" s="69"/>
+      <c r="P54" s="69"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="85"/>
-      <c r="B55" s="85"/>
-      <c r="C55" s="85"/>
-      <c r="D55" s="85"/>
-      <c r="E55" s="85"/>
-      <c r="F55" s="85"/>
-      <c r="G55" s="85"/>
-      <c r="H55" s="85"/>
-      <c r="I55" s="85"/>
-      <c r="J55" s="85"/>
-      <c r="K55" s="85"/>
-      <c r="L55" s="85"/>
-      <c r="M55" s="85"/>
-      <c r="N55" s="85"/>
-      <c r="O55" s="85"/>
-      <c r="P55" s="85"/>
+      <c r="A55" s="69"/>
+      <c r="B55" s="69"/>
+      <c r="C55" s="69"/>
+      <c r="D55" s="69"/>
+      <c r="E55" s="69"/>
+      <c r="F55" s="69"/>
+      <c r="G55" s="69"/>
+      <c r="H55" s="69"/>
+      <c r="I55" s="69"/>
+      <c r="J55" s="69"/>
+      <c r="K55" s="69"/>
+      <c r="L55" s="69"/>
+      <c r="M55" s="69"/>
+      <c r="N55" s="69"/>
+      <c r="O55" s="69"/>
+      <c r="P55" s="69"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="85"/>
-      <c r="B56" s="85"/>
-      <c r="C56" s="85"/>
-      <c r="D56" s="85"/>
-      <c r="E56" s="85"/>
-      <c r="F56" s="85"/>
-      <c r="G56" s="85"/>
-      <c r="H56" s="85"/>
-      <c r="I56" s="85"/>
-      <c r="J56" s="85"/>
-      <c r="K56" s="85"/>
-      <c r="L56" s="85"/>
-      <c r="M56" s="85"/>
-      <c r="N56" s="85"/>
-      <c r="O56" s="85"/>
-      <c r="P56" s="85"/>
+      <c r="A56" s="69"/>
+      <c r="B56" s="69"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
+      <c r="E56" s="69"/>
+      <c r="F56" s="69"/>
+      <c r="G56" s="69"/>
+      <c r="H56" s="69"/>
+      <c r="I56" s="69"/>
+      <c r="J56" s="69"/>
+      <c r="K56" s="69"/>
+      <c r="L56" s="69"/>
+      <c r="M56" s="69"/>
+      <c r="N56" s="69"/>
+      <c r="O56" s="69"/>
+      <c r="P56" s="69"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="85"/>
-      <c r="B57" s="85"/>
-      <c r="C57" s="85"/>
-      <c r="D57" s="85"/>
-      <c r="E57" s="85"/>
-      <c r="F57" s="85"/>
-      <c r="G57" s="85"/>
-      <c r="H57" s="85"/>
-      <c r="I57" s="85"/>
-      <c r="J57" s="85"/>
-      <c r="K57" s="85"/>
-      <c r="L57" s="85"/>
-      <c r="M57" s="85"/>
-      <c r="N57" s="85"/>
-      <c r="O57" s="85"/>
-      <c r="P57" s="85"/>
+      <c r="A57" s="69"/>
+      <c r="B57" s="69"/>
+      <c r="C57" s="69"/>
+      <c r="D57" s="69"/>
+      <c r="E57" s="69"/>
+      <c r="F57" s="69"/>
+      <c r="G57" s="69"/>
+      <c r="H57" s="69"/>
+      <c r="I57" s="69"/>
+      <c r="J57" s="69"/>
+      <c r="K57" s="69"/>
+      <c r="L57" s="69"/>
+      <c r="M57" s="69"/>
+      <c r="N57" s="69"/>
+      <c r="O57" s="69"/>
+      <c r="P57" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="A22:M22"/>
     <mergeCell ref="A54:P57"/>
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A34:M34"/>
+    <mergeCell ref="A48:M48"/>
+    <mergeCell ref="A30:M30"/>
+    <mergeCell ref="A24:M24"/>
+    <mergeCell ref="A49:M49"/>
+    <mergeCell ref="A36:M36"/>
+    <mergeCell ref="A45:M45"/>
+    <mergeCell ref="A46:M46"/>
+    <mergeCell ref="A50:M50"/>
+    <mergeCell ref="A47:M47"/>
+    <mergeCell ref="A42:M42"/>
+    <mergeCell ref="A35:M35"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="A1:P3"/>
+    <mergeCell ref="A17:M18"/>
+    <mergeCell ref="A8:M11"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A41:M41"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A27:M27"/>
     <mergeCell ref="A21:M21"/>
-    <mergeCell ref="A22:M22"/>
-    <mergeCell ref="A23:M23"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="A45:M45"/>
-    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A15:M16"/>
+    <mergeCell ref="A33:M33"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A20:M20"/>
     <mergeCell ref="A38:M38"/>
     <mergeCell ref="A28:M28"/>
-    <mergeCell ref="A34:M34"/>
-    <mergeCell ref="A50:M50"/>
-    <mergeCell ref="A42:M42"/>
-    <mergeCell ref="A46:M46"/>
-    <mergeCell ref="A47:M47"/>
-    <mergeCell ref="A48:M48"/>
-    <mergeCell ref="A49:M49"/>
-    <mergeCell ref="A1:P3"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="A8:M11"/>
-    <mergeCell ref="A7:M7"/>
     <mergeCell ref="A5:P5"/>
     <mergeCell ref="A14:M14"/>
-    <mergeCell ref="A15:M16"/>
-    <mergeCell ref="A19:M19"/>
-    <mergeCell ref="A20:M20"/>
-    <mergeCell ref="A17:M18"/>
-    <mergeCell ref="A30:M30"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A33:M33"/>
-    <mergeCell ref="A29:M29"/>
-    <mergeCell ref="A41:M41"/>
-    <mergeCell ref="A35:M35"/>
-    <mergeCell ref="A36:M36"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A31:M31"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2146E0A-DAC9-8448-8922-32B7A5F4C863}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor indexed="15"/>
   </sheetPr>
@@ -2823,11 +2550,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
+      <c r="A1" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -2842,11 +2569,11 @@
       <c r="Q1" s="2"/>
     </row>
     <row r="2" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="104" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
+      <c r="A2" s="76" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
       <c r="F2" s="11"/>
@@ -2863,11 +2590,11 @@
       <c r="Q2" s="2"/>
     </row>
     <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="101" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="101"/>
-      <c r="C3" s="101"/>
+      <c r="A3" s="75" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="12"/>
@@ -2884,11 +2611,11 @@
       <c r="Q3" s="3"/>
     </row>
     <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="101" t="s">
-        <v>105</v>
-      </c>
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
+      <c r="A4" s="75" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
       <c r="D4" s="12"/>
       <c r="E4" s="12"/>
       <c r="F4" s="12"/>
@@ -2905,11 +2632,11 @@
       <c r="Q4" s="4"/>
     </row>
     <row r="5" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="101" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
+      <c r="A5" s="75" t="s">
+        <v>58</v>
+      </c>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="5"/>
@@ -2926,11 +2653,11 @@
       <c r="Q5" s="5"/>
     </row>
     <row r="6" spans="1:24" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="76" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="76"/>
-      <c r="C6" s="76"/>
+      <c r="A6" s="68" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="5"/>
@@ -2947,11 +2674,11 @@
       <c r="Q6" s="5"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="76" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="76"/>
-      <c r="C7" s="76"/>
+      <c r="A7" s="68" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="5"/>
@@ -2987,169 +2714,169 @@
       <c r="Q8" s="5"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A9" s="102" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="103"/>
+      <c r="A9" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="72"/>
       <c r="C9" s="54">
         <v>360</v>
       </c>
     </row>
     <row r="10" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="93" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="93"/>
+      <c r="A10" s="70" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="67"/>
       <c r="C10" s="13"/>
-      <c r="D10" s="94" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="95"/>
-      <c r="F10" s="95"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="95"/>
-      <c r="J10" s="95"/>
-      <c r="K10" s="95"/>
-      <c r="L10" s="95"/>
-      <c r="M10" s="95"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="96"/>
-      <c r="Q10" s="96"/>
-      <c r="R10" s="96"/>
-      <c r="S10" s="96"/>
-      <c r="T10" s="96"/>
+      <c r="D10" s="78" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
+      <c r="T10" s="67"/>
       <c r="U10" s="13"/>
       <c r="V10" s="13"/>
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
     </row>
     <row r="11" spans="1:24" s="6" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="97" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="98" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="99" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" s="92" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="92"/>
-      <c r="H11" s="92" t="s">
-        <v>63</v>
-      </c>
-      <c r="I11" s="92"/>
-      <c r="J11" s="92" t="s">
+      <c r="A11" s="73" t="s">
         <v>64</v>
       </c>
-      <c r="K11" s="92"/>
-      <c r="L11" s="92" t="s">
+      <c r="B11" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="M11" s="92"/>
-      <c r="N11" s="92" t="s">
+      <c r="C11" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="O11" s="92"/>
-      <c r="P11" s="92" t="s">
+      <c r="D11" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="Q11" s="92"/>
-      <c r="R11" s="92" t="s">
+      <c r="E11" s="67"/>
+      <c r="F11" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="67"/>
+      <c r="H11" s="66" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="67"/>
+      <c r="J11" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="S11" s="92"/>
-      <c r="T11" s="92" t="s">
+      <c r="K11" s="67"/>
+      <c r="L11" s="66" t="s">
         <v>71</v>
       </c>
-      <c r="U11" s="92"/>
-      <c r="V11" s="92" t="s">
+      <c r="M11" s="67"/>
+      <c r="N11" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="W11" s="92"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q11" s="67"/>
+      <c r="R11" s="66" t="s">
+        <v>74</v>
+      </c>
+      <c r="S11" s="67"/>
+      <c r="T11" s="66" t="s">
+        <v>75</v>
+      </c>
+      <c r="U11" s="67"/>
+      <c r="V11" s="66" t="s">
+        <v>76</v>
+      </c>
+      <c r="W11" s="67"/>
       <c r="X11" s="14" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:24" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="97"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="100"/>
+      <c r="A12" s="74"/>
+      <c r="B12" s="74"/>
+      <c r="C12" s="74"/>
       <c r="D12" s="15" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="N12" s="15" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="O12" s="16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="P12" s="15" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Q12" s="16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="S12" s="16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="T12" s="15" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="U12" s="16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="V12" s="15" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="W12" s="16" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="X12" s="14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="26.4" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="64" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="B13" s="63">
         <v>0</v>
@@ -3179,13 +2906,13 @@
     </row>
     <row r="14" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="64" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="B14" s="63">
         <v>2</v>
       </c>
       <c r="C14" s="63" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="D14" s="18">
         <v>44</v>
@@ -3207,9 +2934,13 @@
       </c>
       <c r="J14" s="18"/>
       <c r="K14" s="19"/>
-      <c r="L14" s="18"/>
+      <c r="L14" s="18">
+        <v>35</v>
+      </c>
       <c r="M14" s="19"/>
-      <c r="N14" s="18"/>
+      <c r="N14" s="18">
+        <v>35</v>
+      </c>
       <c r="O14" s="19"/>
       <c r="P14" s="18"/>
       <c r="Q14" s="19"/>
@@ -3223,7 +2954,7 @@
     </row>
     <row r="15" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="64" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="B15" s="63">
         <v>0</v>
@@ -3253,7 +2984,7 @@
     </row>
     <row r="16" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="64" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="B16" s="63">
         <v>0</v>
@@ -3283,7 +3014,7 @@
     </row>
     <row r="17" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="64" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="B17" s="63">
         <v>4</v>
@@ -3305,9 +3036,13 @@
       <c r="K17" s="19">
         <v>12</v>
       </c>
-      <c r="L17" s="18"/>
+      <c r="L17" s="18">
+        <v>40</v>
+      </c>
       <c r="M17" s="19"/>
-      <c r="N17" s="18"/>
+      <c r="N17" s="18">
+        <v>40</v>
+      </c>
       <c r="O17" s="19"/>
       <c r="P17" s="18"/>
       <c r="Q17" s="19"/>
@@ -3321,7 +3056,7 @@
     </row>
     <row r="18" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="64" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="B18" s="63">
         <v>0</v>
@@ -3339,9 +3074,13 @@
       <c r="K18" s="19">
         <v>3</v>
       </c>
-      <c r="L18" s="18"/>
+      <c r="L18" s="18">
+        <v>5</v>
+      </c>
       <c r="M18" s="19"/>
-      <c r="N18" s="18"/>
+      <c r="N18" s="18">
+        <v>5</v>
+      </c>
       <c r="O18" s="19"/>
       <c r="P18" s="18"/>
       <c r="Q18" s="19"/>
@@ -3355,13 +3094,13 @@
     </row>
     <row r="19" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="64" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="B19" s="63">
         <v>2</v>
       </c>
       <c r="C19" s="63" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="D19" s="18">
         <v>20</v>
@@ -3387,10 +3126,18 @@
       <c r="K19" s="19">
         <v>1.75</v>
       </c>
-      <c r="L19" s="18"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="19"/>
+      <c r="L19" s="18">
+        <v>15</v>
+      </c>
+      <c r="M19" s="19">
+        <v>1</v>
+      </c>
+      <c r="N19" s="18">
+        <v>15</v>
+      </c>
+      <c r="O19" s="19">
+        <v>1</v>
+      </c>
       <c r="P19" s="18"/>
       <c r="Q19" s="19"/>
       <c r="R19" s="18"/>
@@ -3403,13 +3150,13 @@
     </row>
     <row r="20" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="64" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="B20" s="63">
         <v>2</v>
       </c>
       <c r="C20" s="63" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="D20" s="18">
         <v>60</v>
@@ -3435,10 +3182,18 @@
       <c r="K20" s="19">
         <v>6</v>
       </c>
-      <c r="L20" s="18"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="19"/>
+      <c r="L20" s="18">
+        <v>40</v>
+      </c>
+      <c r="M20" s="19">
+        <v>15.33</v>
+      </c>
+      <c r="N20" s="18">
+        <v>40</v>
+      </c>
+      <c r="O20" s="19">
+        <v>5.25</v>
+      </c>
       <c r="P20" s="18"/>
       <c r="Q20" s="19"/>
       <c r="R20" s="18"/>
@@ -3451,7 +3206,7 @@
     </row>
     <row r="21" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="64" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="B21" s="63">
         <v>0</v>
@@ -3481,13 +3236,13 @@
     </row>
     <row r="22" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="62" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="B22" s="63">
         <v>2</v>
       </c>
       <c r="C22" s="63" t="s">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="D22" s="18">
         <v>60</v>
@@ -3513,10 +3268,18 @@
       <c r="K22" s="19">
         <v>0</v>
       </c>
-      <c r="L22" s="18"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="19"/>
+      <c r="L22" s="18">
+        <v>0</v>
+      </c>
+      <c r="M22" s="19">
+        <v>0</v>
+      </c>
+      <c r="N22" s="18">
+        <v>0</v>
+      </c>
+      <c r="O22" s="19">
+        <v>0</v>
+      </c>
       <c r="P22" s="18"/>
       <c r="Q22" s="19"/>
       <c r="R22" s="18"/>
@@ -3529,13 +3292,13 @@
     </row>
     <row r="23" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="62" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="B23" s="63">
         <v>2</v>
       </c>
       <c r="C23" s="63" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="D23" s="18"/>
       <c r="E23" s="19"/>
@@ -3571,13 +3334,13 @@
     </row>
     <row r="24" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="62" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="B24" s="63">
         <v>3</v>
       </c>
       <c r="C24" s="63" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="D24" s="18"/>
       <c r="E24" s="19"/>
@@ -3595,9 +3358,13 @@
       </c>
       <c r="J24" s="18"/>
       <c r="K24" s="19"/>
-      <c r="L24" s="18"/>
+      <c r="L24" s="18">
+        <v>3</v>
+      </c>
       <c r="M24" s="19"/>
-      <c r="N24" s="18"/>
+      <c r="N24" s="18">
+        <v>3</v>
+      </c>
       <c r="O24" s="19"/>
       <c r="P24" s="18"/>
       <c r="Q24" s="19"/>
@@ -3610,13 +3377,19 @@
       <c r="X24" s="17"/>
     </row>
     <row r="25" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="62"/>
-      <c r="B25" s="63"/>
-      <c r="C25" s="63"/>
+      <c r="A25" s="62" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="63">
+        <v>7</v>
+      </c>
+      <c r="C25" s="63" t="s">
+        <v>97</v>
+      </c>
       <c r="D25" s="18"/>
       <c r="E25" s="19"/>
       <c r="F25" s="18"/>
-      <c r="G25" s="17"/>
+      <c r="G25" s="19"/>
       <c r="H25" s="18"/>
       <c r="I25" s="19"/>
       <c r="J25" s="18"/>
@@ -3624,7 +3397,9 @@
       <c r="L25" s="18"/>
       <c r="M25" s="19"/>
       <c r="N25" s="18"/>
-      <c r="O25" s="19"/>
+      <c r="O25" s="19">
+        <v>16.829999999999998</v>
+      </c>
       <c r="P25" s="18"/>
       <c r="Q25" s="19"/>
       <c r="R25" s="18"/>
@@ -3741,7 +3516,7 @@
     </row>
     <row r="30" spans="1:24" s="57" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="56" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="B30" s="56"/>
       <c r="C30" s="56"/>
@@ -3750,11 +3525,11 @@
         <v>140</v>
       </c>
       <c r="E30" s="56">
-        <f>SUM(E13:E29)</f>
+        <f t="shared" ref="E30:W30" si="0">SUM(E13:E29)</f>
         <v>18</v>
       </c>
       <c r="F30" s="56">
-        <f t="shared" ref="F30:W30" si="0">SUM(F13:F29)</f>
+        <f t="shared" si="0"/>
         <v>186.75</v>
       </c>
       <c r="G30" s="56">
@@ -3779,19 +3554,19 @@
       </c>
       <c r="L30" s="56">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="M30" s="56">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16.329999999999998</v>
       </c>
       <c r="N30" s="56">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="O30" s="56">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23.08</v>
       </c>
       <c r="P30" s="56">
         <f t="shared" si="0"/>
@@ -3877,39 +3652,37 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="D10:T10"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="V11:W11"/>
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="A4:C4"/>
     <mergeCell ref="H11:I11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="D10:T10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="V11:W11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="R11:S11"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F01C0A0-4437-8143-8371-182371F45606}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor indexed="13"/>
   </sheetPr>
@@ -3930,394 +3703,394 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
+      <c r="A1" s="85" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
       <c r="E1" s="22"/>
     </row>
-    <row r="2" spans="1:47" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A2" s="108" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
+    <row r="2" spans="1:47" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="96" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
       <c r="E2" s="23"/>
     </row>
-    <row r="3" spans="1:47" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A3" s="108" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" s="108"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
+    <row r="3" spans="1:47" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="96" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
       <c r="E3" s="23"/>
     </row>
-    <row r="4" spans="1:47" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="61" t="s">
-        <v>13</v>
+        <v>99</v>
       </c>
       <c r="B4" s="59"/>
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
       <c r="E4" s="23"/>
     </row>
-    <row r="5" spans="1:47" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A5" s="108" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
+    <row r="5" spans="1:47" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="96" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="69"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="69"/>
       <c r="E5" s="23"/>
     </row>
     <row r="6" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A6" s="88" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="88"/>
-      <c r="D6" s="88"/>
+      <c r="A6" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
       <c r="E6" s="22"/>
     </row>
     <row r="7" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A7" s="108" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
+      <c r="A7" s="96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
       <c r="E7" s="22"/>
     </row>
     <row r="8" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A8" s="88" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="88"/>
-      <c r="C8" s="88"/>
-      <c r="D8" s="88"/>
+      <c r="A8" s="85" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="69"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="69"/>
       <c r="E8" s="22"/>
     </row>
     <row r="9" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A9" s="88" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="88"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="88"/>
+      <c r="A9" s="85" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="69"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
       <c r="E9" s="22"/>
     </row>
     <row r="10" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A10" s="88" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="88"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
+      <c r="A10" s="85" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="69"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
       <c r="E10" s="22"/>
     </row>
     <row r="11" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A11" s="88" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="88"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88"/>
+      <c r="A11" s="85" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="69"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
       <c r="E11" s="22"/>
     </row>
     <row r="12" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A12" s="88"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="88"/>
-      <c r="D12" s="88"/>
+      <c r="A12" s="85"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
       <c r="E12" s="22"/>
     </row>
     <row r="13" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A13" s="112" t="str">
+      <c r="A13" s="97" t="str">
         <f>IF(AND(COUNT(D17:D68) &gt;0,(D69&lt;&gt;100)),"Value does not sum to $100","Value is OK")</f>
         <v>Value is OK</v>
       </c>
-      <c r="B13" s="113"/>
-      <c r="C13" s="113"/>
-      <c r="D13" s="114"/>
+      <c r="B13" s="72"/>
+      <c r="C13" s="72"/>
+      <c r="D13" s="67"/>
     </row>
     <row r="14" spans="1:47" s="21" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="66" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="66" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="66" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" s="66" t="s">
-        <v>102</v>
-      </c>
-      <c r="E14" s="109" t="s">
-        <v>103</v>
-      </c>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="110"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="110"/>
-      <c r="P14" s="110"/>
-      <c r="Q14" s="110"/>
-      <c r="R14" s="110"/>
-      <c r="S14" s="110"/>
-      <c r="T14" s="110"/>
-      <c r="U14" s="110"/>
-      <c r="V14" s="110"/>
-      <c r="W14" s="110"/>
-      <c r="X14" s="110"/>
-      <c r="Y14" s="110"/>
-      <c r="Z14" s="110"/>
-      <c r="AA14" s="110"/>
-      <c r="AB14" s="110"/>
-      <c r="AC14" s="110"/>
-      <c r="AD14" s="110"/>
-      <c r="AE14" s="110"/>
-      <c r="AF14" s="110"/>
-      <c r="AG14" s="110"/>
-      <c r="AH14" s="110"/>
-      <c r="AI14" s="110"/>
-      <c r="AJ14" s="110"/>
-      <c r="AK14" s="110"/>
-      <c r="AL14" s="110"/>
-      <c r="AM14" s="110"/>
-      <c r="AN14" s="110"/>
-      <c r="AO14" s="110"/>
-      <c r="AP14" s="110"/>
-      <c r="AQ14" s="110"/>
-      <c r="AR14" s="111"/>
+      <c r="A14" s="94" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="94" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="94" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="94" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="94" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="72"/>
+      <c r="V14" s="72"/>
+      <c r="W14" s="72"/>
+      <c r="X14" s="72"/>
+      <c r="Y14" s="72"/>
+      <c r="Z14" s="72"/>
+      <c r="AA14" s="72"/>
+      <c r="AB14" s="72"/>
+      <c r="AC14" s="72"/>
+      <c r="AD14" s="72"/>
+      <c r="AE14" s="72"/>
+      <c r="AF14" s="72"/>
+      <c r="AG14" s="72"/>
+      <c r="AH14" s="72"/>
+      <c r="AI14" s="72"/>
+      <c r="AJ14" s="72"/>
+      <c r="AK14" s="72"/>
+      <c r="AL14" s="72"/>
+      <c r="AM14" s="72"/>
+      <c r="AN14" s="72"/>
+      <c r="AO14" s="72"/>
+      <c r="AP14" s="72"/>
+      <c r="AQ14" s="72"/>
+      <c r="AR14" s="67"/>
       <c r="AS14" s="25"/>
       <c r="AT14" s="25"/>
       <c r="AU14" s="25" t="s">
-        <v>9</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:47" s="1" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="117"/>
-      <c r="B15" s="115"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="66" t="s">
-        <v>88</v>
-      </c>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66" t="s">
-        <v>89</v>
-      </c>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="94" t="s">
-        <v>90</v>
-      </c>
-      <c r="N15" s="94"/>
-      <c r="O15" s="94"/>
-      <c r="P15" s="94"/>
-      <c r="Q15" s="66" t="s">
-        <v>91</v>
-      </c>
-      <c r="R15" s="66"/>
-      <c r="S15" s="66"/>
-      <c r="T15" s="66"/>
-      <c r="U15" s="66" t="s">
-        <v>92</v>
-      </c>
-      <c r="V15" s="66"/>
-      <c r="W15" s="66"/>
-      <c r="X15" s="66"/>
-      <c r="Y15" s="66" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z15" s="66"/>
-      <c r="AA15" s="66"/>
-      <c r="AB15" s="66"/>
-      <c r="AC15" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD15" s="66"/>
-      <c r="AE15" s="66"/>
-      <c r="AF15" s="66"/>
-      <c r="AG15" s="66" t="s">
-        <v>95</v>
-      </c>
-      <c r="AH15" s="66"/>
-      <c r="AI15" s="66"/>
-      <c r="AJ15" s="66"/>
-      <c r="AK15" s="66" t="s">
-        <v>96</v>
-      </c>
-      <c r="AL15" s="66"/>
-      <c r="AM15" s="66"/>
-      <c r="AN15" s="66"/>
-      <c r="AO15" s="66" t="s">
-        <v>97</v>
-      </c>
-      <c r="AP15" s="66"/>
-      <c r="AQ15" s="66"/>
-      <c r="AR15" s="66"/>
-      <c r="AS15" s="105" t="s">
-        <v>10</v>
-      </c>
-      <c r="AT15" s="105" t="s">
-        <v>11</v>
-      </c>
-      <c r="AU15" s="105" t="s">
-        <v>12</v>
+      <c r="A15" s="95"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="94" t="s">
+        <v>109</v>
+      </c>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="94" t="s">
+        <v>110</v>
+      </c>
+      <c r="J15" s="72"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="N15" s="72"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
+      <c r="T15" s="67"/>
+      <c r="U15" s="94" t="s">
+        <v>113</v>
+      </c>
+      <c r="V15" s="72"/>
+      <c r="W15" s="72"/>
+      <c r="X15" s="67"/>
+      <c r="Y15" s="94" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z15" s="72"/>
+      <c r="AA15" s="72"/>
+      <c r="AB15" s="67"/>
+      <c r="AC15" s="94" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD15" s="72"/>
+      <c r="AE15" s="72"/>
+      <c r="AF15" s="67"/>
+      <c r="AG15" s="94" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH15" s="72"/>
+      <c r="AI15" s="72"/>
+      <c r="AJ15" s="67"/>
+      <c r="AK15" s="94" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL15" s="72"/>
+      <c r="AM15" s="72"/>
+      <c r="AN15" s="67"/>
+      <c r="AO15" s="94" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP15" s="72"/>
+      <c r="AQ15" s="72"/>
+      <c r="AR15" s="67"/>
+      <c r="AS15" s="78" t="s">
+        <v>119</v>
+      </c>
+      <c r="AT15" s="78" t="s">
+        <v>120</v>
+      </c>
+      <c r="AU15" s="78" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:47" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="117"/>
-      <c r="B16" s="115"/>
-      <c r="C16" s="116"/>
-      <c r="D16" s="117"/>
+      <c r="A16" s="74"/>
+      <c r="B16" s="74"/>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
       <c r="E16" s="29" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F16" s="27" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="G16" s="30" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="I16" s="29" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="J16" s="27" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="K16" s="30" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="L16" s="28" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="M16" s="29" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="N16" s="27" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="O16" s="30" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="P16" s="28" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="Q16" s="29" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="R16" s="27" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="S16" s="30" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="T16" s="28" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="U16" s="29" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="V16" s="27" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="W16" s="30" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="X16" s="28" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="Y16" s="29" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="Z16" s="27" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AA16" s="30" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="AB16" s="28" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="AC16" s="26" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="AD16" s="27" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AE16" s="30" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="AF16" s="28" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="AG16" s="29" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="AH16" s="27" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AI16" s="30" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="AJ16" s="28" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="AK16" s="29" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="AL16" s="27" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AM16" s="30" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="AN16" s="28" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="AO16" s="29" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="AP16" s="27" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="AQ16" s="30" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="AR16" s="28" t="s">
-        <v>101</v>
-      </c>
-      <c r="AS16" s="107"/>
-      <c r="AT16" s="107"/>
-      <c r="AU16" s="106"/>
+        <v>125</v>
+      </c>
+      <c r="AS16" s="74"/>
+      <c r="AT16" s="74"/>
+      <c r="AU16" s="74"/>
     </row>
     <row r="17" spans="1:47" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B17" s="17">
         <v>3</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D17" s="17"/>
       <c r="I17" s="20">
@@ -4368,10 +4141,18 @@
       <c r="X17" s="17">
         <v>0</v>
       </c>
-      <c r="Y17" s="20"/>
-      <c r="Z17" s="17"/>
-      <c r="AA17" s="20"/>
-      <c r="AB17" s="17"/>
+      <c r="Y17" s="20">
+        <v>10</v>
+      </c>
+      <c r="Z17" s="17">
+        <v>6.5</v>
+      </c>
+      <c r="AA17" s="20">
+        <v>2</v>
+      </c>
+      <c r="AB17" s="17">
+        <v>4.5</v>
+      </c>
       <c r="AC17" s="20"/>
       <c r="AD17" s="17"/>
       <c r="AE17" s="20"/>
@@ -4396,13 +4177,13 @@
     </row>
     <row r="18" spans="1:47" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B18" s="17">
         <v>3</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D18" s="17"/>
       <c r="I18" s="20">
@@ -4453,10 +4234,18 @@
       <c r="X18" s="17">
         <v>1</v>
       </c>
-      <c r="Y18" s="20"/>
-      <c r="Z18" s="17"/>
-      <c r="AA18" s="20"/>
-      <c r="AB18" s="17"/>
+      <c r="Y18" s="20">
+        <v>10</v>
+      </c>
+      <c r="Z18" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="20">
+        <v>2</v>
+      </c>
+      <c r="AB18" s="17">
+        <v>0</v>
+      </c>
       <c r="AC18" s="20"/>
       <c r="AD18" s="17"/>
       <c r="AE18" s="20"/>
@@ -6931,24 +6720,24 @@
     </row>
     <row r="69" spans="1:47" s="35" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="34" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="B69" s="34"/>
       <c r="C69" s="34"/>
       <c r="D69" s="34">
-        <f>SUM(D17:D68)</f>
+        <f t="shared" ref="D69:AR69" si="0">SUM(D17:D68)</f>
         <v>0</v>
       </c>
       <c r="E69" s="34">
-        <f>SUM(E17:E68)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F69" s="34">
-        <f>SUM(F17:F68)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G69" s="34">
-        <f t="shared" ref="G69:AR69" si="0">SUM(G17:G68)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H69" s="34">
@@ -6956,19 +6745,19 @@
         <v>0</v>
       </c>
       <c r="I69" s="34">
-        <f>SUM(I17:I68)</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="J69" s="34">
-        <f>SUM(J17:J68)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K69" s="34">
-        <f>SUM(K17:K68)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="L69" s="34">
-        <f>SUM(L17:L68)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M69" s="34">
@@ -7021,19 +6810,19 @@
       </c>
       <c r="Y69" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z69" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA69" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB69" s="34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AC69" s="34">
         <f t="shared" si="0"/>
@@ -7105,38 +6894,37 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AK15:AN15"/>
-    <mergeCell ref="AO15:AR15"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="AG15:AJ15"/>
     <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="AU15:AU16"/>
     <mergeCell ref="D14:D16"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="U15:X15"/>
     <mergeCell ref="Y15:AB15"/>
+    <mergeCell ref="Q15:T15"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="AT15:AT16"/>
+    <mergeCell ref="AK15:AN15"/>
     <mergeCell ref="AC15:AF15"/>
-    <mergeCell ref="AG15:AJ15"/>
+    <mergeCell ref="E14:AR14"/>
+    <mergeCell ref="AO15:AR15"/>
+    <mergeCell ref="AS15:AS16"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="B14:B16"/>
     <mergeCell ref="E15:H15"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="AU15:AU16"/>
-    <mergeCell ref="AS15:AS16"/>
-    <mergeCell ref="AT15:AT16"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="E14:AR14"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="Q15:T15"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="I15:L15"/>
     <mergeCell ref="M15:P15"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A13">
     <cfRule type="cellIs" dxfId="16" priority="1" stopIfTrue="1" operator="equal">
       <formula>"Value does not sum to $100"</formula>
@@ -7147,12 +6935,11 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8665904F-8616-1D44-9978-BDA850D9B29C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor indexed="11"/>
   </sheetPr>
@@ -7164,7 +6951,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -7180,8 +6967,8 @@
       <c r="M1" s="3"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="67" t="s">
-        <v>26</v>
+      <c r="A2" s="92" t="s">
+        <v>47</v>
       </c>
       <c r="B2" s="47"/>
       <c r="C2" s="47"/>
@@ -7197,7 +6984,7 @@
       <c r="M2" s="47"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="68"/>
+      <c r="A3" s="69"/>
       <c r="B3" s="47"/>
       <c r="C3" s="47"/>
       <c r="D3" s="47"/>
@@ -7212,7 +6999,7 @@
       <c r="M3" s="47"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="68"/>
+      <c r="A4" s="69"/>
       <c r="B4" s="7"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -7225,61 +7012,61 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="48"/>
-      <c r="B7" s="66" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="66"/>
-      <c r="K7" s="66"/>
+      <c r="B7" s="94" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="67"/>
       <c r="L7" s="17"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G8" s="31" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K8" s="31" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L8" s="36" t="s">
-        <v>28</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="B9" s="17">
         <v>5</v>
@@ -7296,19 +7083,21 @@
       <c r="F9" s="17">
         <v>2</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="20">
+        <v>8.5</v>
+      </c>
       <c r="H9" s="17"/>
       <c r="I9" s="20"/>
       <c r="J9" s="17"/>
       <c r="K9" s="20"/>
       <c r="L9" s="34">
-        <f>SUM(B9:K9)</f>
-        <v>25.25</v>
+        <f t="shared" ref="L9:L18" si="0">SUM(B9:K9)</f>
+        <v>33.75</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="B10" s="17">
         <v>1.75</v>
@@ -7323,21 +7112,23 @@
         <v>3</v>
       </c>
       <c r="F10" s="17">
-        <v>2</v>
-      </c>
-      <c r="G10" s="20"/>
+        <v>3</v>
+      </c>
+      <c r="G10" s="20">
+        <v>10.83</v>
+      </c>
       <c r="H10" s="17"/>
       <c r="I10" s="20"/>
       <c r="J10" s="17"/>
       <c r="K10" s="20"/>
       <c r="L10" s="34">
-        <f t="shared" ref="L10:L15" si="0">SUM(B10:K10)</f>
-        <v>14.25</v>
+        <f t="shared" si="0"/>
+        <v>26.08</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="B11" s="17">
         <v>1.75</v>
@@ -7352,21 +7143,23 @@
         <v>5.5</v>
       </c>
       <c r="F11" s="17">
-        <v>4.5</v>
-      </c>
-      <c r="G11" s="20"/>
+        <v>3.5</v>
+      </c>
+      <c r="G11" s="20">
+        <v>3</v>
+      </c>
       <c r="H11" s="17"/>
       <c r="I11" s="20"/>
       <c r="J11" s="17"/>
       <c r="K11" s="20"/>
       <c r="L11" s="34">
         <f t="shared" si="0"/>
-        <v>22.25</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="B12" s="17">
         <v>1.75</v>
@@ -7383,19 +7176,21 @@
       <c r="F12" s="17">
         <v>2</v>
       </c>
-      <c r="G12" s="20"/>
+      <c r="G12" s="20">
+        <v>2.5</v>
+      </c>
       <c r="H12" s="17"/>
       <c r="I12" s="20"/>
       <c r="J12" s="17"/>
       <c r="K12" s="20"/>
       <c r="L12" s="34">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="B13" s="17">
         <v>4</v>
@@ -7410,21 +7205,23 @@
         <v>5.6</v>
       </c>
       <c r="F13" s="17">
-        <v>2</v>
-      </c>
-      <c r="G13" s="20"/>
+        <v>3.5</v>
+      </c>
+      <c r="G13" s="20">
+        <v>6.5</v>
+      </c>
       <c r="H13" s="17"/>
       <c r="I13" s="20"/>
       <c r="J13" s="17"/>
       <c r="K13" s="20"/>
       <c r="L13" s="34">
         <f t="shared" si="0"/>
-        <v>21.1</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B14" s="17">
         <v>3</v>
@@ -7438,15 +7235,19 @@
       <c r="E14" s="20">
         <v>7.8</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="20"/>
+      <c r="F14" s="17">
+        <v>2.33</v>
+      </c>
+      <c r="G14" s="20">
+        <v>5.75</v>
+      </c>
       <c r="H14" s="17"/>
       <c r="I14" s="20"/>
       <c r="J14" s="17"/>
       <c r="K14" s="20"/>
       <c r="L14" s="34">
         <f t="shared" si="0"/>
-        <v>22.3</v>
+        <v>30.380000000000003</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -7479,7 +7280,7 @@
       <c r="J16" s="17"/>
       <c r="K16" s="20"/>
       <c r="L16" s="34">
-        <f>SUM(B16:K16)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7496,7 +7297,7 @@
       <c r="J17" s="17"/>
       <c r="K17" s="20"/>
       <c r="L17" s="34">
-        <f>SUM(B17:K17)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -7513,24 +7314,22 @@
       <c r="J18" s="17"/>
       <c r="K18" s="20"/>
       <c r="L18" s="34">
-        <f>SUM(B18:K18)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:A4"/>
     <mergeCell ref="B7:K7"/>
-    <mergeCell ref="A2:A4"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535E69F9-F41B-E54C-AE8B-D87B1A419256}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor indexed="52"/>
   </sheetPr>
@@ -7545,41 +7344,41 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="38"/>
       <c r="P1" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="41" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <f>60*(10-(COUNTBLANK(PerPerson!A9:A18)))</f>
         <v>360</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="D2" s="40"/>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <f>SUM('General Tasks'!E30,'General Tasks'!G30,'General Tasks'!I30,'General Tasks'!K30,'General Tasks'!M30,'General Tasks'!O30,'General Tasks'!Q30,'General Tasks'!S30,'General Tasks'!U30,'General Tasks'!W30,Requirements!F69,Requirements!H69,Requirements!J69,Requirements!L69,Requirements!N69,Requirements!P69,Requirements!R69,Requirements!T69,Requirements!V69,Requirements!X69,Requirements!Z69,Requirements!AB69,Requirements!AD69,Requirements!AF69,Requirements!AH69,Requirements!AJ69,Requirements!AL69,Requirements!AN69,Requirements!AP69,Requirements!AR69)</f>
-        <v>120.25</v>
+        <v>173.66</v>
       </c>
       <c r="D3" s="40"/>
       <c r="P3">
@@ -7593,11 +7392,11 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <f>B2-B3</f>
-        <v>239.75</v>
+        <v>186.34</v>
       </c>
       <c r="C4" t="str">
         <f>IF(B4&gt;=0,"within budget","over budget")</f>
@@ -7615,11 +7414,11 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <f>(('General Tasks'!C9)-B3)</f>
-        <v>239.75</v>
+        <v>186.34</v>
       </c>
       <c r="C5" t="str">
         <f>IF(B5&gt;=0,"within budget","over budget")</f>
@@ -7629,18 +7428,18 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <f>(SUM('General Tasks'!H30,Requirements!M69,Requirements!O69) - (B3))</f>
-        <v>159.75</v>
+        <v>106.34</v>
       </c>
       <c r="C6" t="str">
         <f>IF(B6&gt;=0,"within estimate","over estimate")</f>
         <v>within estimate</v>
       </c>
       <c r="D6" s="40" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <f>IF(Requirements!AT19,Requirements!D19,0)</f>
@@ -7653,18 +7452,18 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" s="43">
         <f>(SUM('General Tasks'!P30,Requirements!AC69,Requirements!AE69) - (B4))</f>
-        <v>-239.75</v>
+        <v>-186.34</v>
       </c>
       <c r="C7" s="43" t="str">
         <f>IF(B7&gt;=0,"within estimate","over estimate")</f>
         <v>over estimate</v>
       </c>
       <c r="D7" s="44" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -7700,7 +7499,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="45" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B11" s="37"/>
       <c r="C11" s="38"/>
@@ -7715,7 +7514,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <f>COUNT(Requirements!AT17:AT68)</f>
@@ -7733,7 +7532,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <f>P58</f>
@@ -7754,7 +7553,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <f>COUNT(Requirements!AS17:AS68)</f>
@@ -7772,7 +7571,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="42" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="B15" s="43">
         <f>Q58</f>
@@ -7823,7 +7622,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="45" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="B19" s="38"/>
       <c r="P19">
@@ -7837,7 +7636,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B20" s="40">
         <f>COUNT('General Tasks'!X13:X29)</f>
@@ -7854,11 +7653,11 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="46" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B21" s="44">
         <f>(COUNT('General Tasks'!B18:B29)-B20)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <f>IF(Requirements!AT33,Requirements!D33,0)</f>
@@ -8240,7 +8039,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B4:B5">
     <cfRule type="cellIs" dxfId="14" priority="1" stopIfTrue="1" operator="greaterThanOrEqual">
       <formula>0</formula>
@@ -8305,6 +8103,5 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>